--- a/artfynd/A 13344-2024 artfynd.xlsx
+++ b/artfynd/A 13344-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117455596</v>
       </c>
       <c r="B2" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>117455597</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>117455592</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
